--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2022_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2022_magallanes.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:40</t>
+    <t xml:space="preserve">2026-09-24 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -727,7 +727,7 @@
         <v>0.03</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.32</v>
@@ -750,7 +750,7 @@
         <v>0.03</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.76</v>
@@ -773,7 +773,7 @@
         <v>0.02</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.51</v>
@@ -787,7 +787,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.76</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>6</v>
@@ -796,10 +796,10 @@
         <v>0.01</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="14">
@@ -833,19 +833,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.69</v>
+        <v>0.77</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>309</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="16">
@@ -856,7 +856,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>6</v>
@@ -868,7 +868,7 @@
         <v>309</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="17">
@@ -879,19 +879,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.28</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>309</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.81</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="18">
